--- a/Submission/1EME_TG_AP_Submission.xlsx
+++ b/Submission/1EME_TG_AP_Submission.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/theloniousgoerz/Academic/Projects/_One_Offs/1eme/Submission/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{455BA2FE-7429-7C41-B9D3-B4A7BE50E85F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1005750F-67A2-A546-9F16-E7B03F862B22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="5" xr2:uid="{F2A3ED0D-6A90-4E3C-AFB4-F94EBA268CA3}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17140" activeTab="3" xr2:uid="{F2A3ED0D-6A90-4E3C-AFB4-F94EBA268CA3}"/>
   </bookViews>
   <sheets>
     <sheet name="Estimates 1 (total by state)" sheetId="1" r:id="rId1"/>
@@ -970,7 +970,7 @@
       <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="4">
         <v>107874</v>
       </c>
       <c r="D2" s="3">
@@ -987,7 +987,7 @@
       <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="4">
         <v>5838</v>
       </c>
       <c r="D3" s="3">
